--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,112 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128340042</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Manjärvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>745336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7269600</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>128340042</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80987712</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745189.1837913083</v>
+        <v>745189</v>
       </c>
       <c r="R2" t="n">
-        <v>7269722.849999492</v>
+        <v>7269723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-08-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80987765</v>
+        <v>80987755</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745192.0552362205</v>
+        <v>745101</v>
       </c>
       <c r="R3" t="n">
-        <v>7269802.864262083</v>
+        <v>7269824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-08-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80987755</v>
+        <v>80987765</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745101.2093184444</v>
+        <v>745192</v>
       </c>
       <c r="R4" t="n">
-        <v>7269824.024135397</v>
+        <v>7269803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-08-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80987733</v>
+        <v>128340042</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åbyälven, Nb</t>
+          <t>Manjärvträsk, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745203.8904608734</v>
+        <v>745336</v>
       </c>
       <c r="R5" t="n">
-        <v>7269722.001584216</v>
+        <v>7269600</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1035,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81149362</v>
+        <v>80987733</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Markbygden, Nb</t>
+          <t>Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745150.9610945407</v>
+        <v>745204</v>
       </c>
       <c r="R6" t="n">
-        <v>7269829.052878227</v>
+        <v>7269722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,27 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Markbygden, Ecogain på uppdrag av Enercon</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,61 +1157,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Oskar Wallströmer</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340042</v>
+        <v>81149362</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Manjärvträsk, Nb</t>
+          <t>Markbygden, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745336</v>
+        <v>745151</v>
       </c>
       <c r="R7" t="n">
-        <v>7269600</v>
+        <v>7269829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,17 +1234,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2019-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2019-08-02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Naturvärdesinventering Markbygden, Ecogain på uppdrag av Enercon</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,12 +1259,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Oskar Wallströmer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 40202-2025 artfynd.xlsx
+++ b/artfynd/A 40202-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987712</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340042</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987733</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81149362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>